--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/BOMBA ÓLEO - 26_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/BOMBA ÓLEO - 26_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,136 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TAMPA RETOR BOMBA OLEO EMBUS TITAN/ TODAY 10065-E</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>14</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>10765</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>RETOR BOMBA OLEO SOLIDEZ TITAN CG150/ XR190-300</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>7899468062247</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>RETOR BOMBA OLEO AUDAX BROS NXR160/ TITAN FAN160/ XRE190</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>16</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>7899468040498</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>RETOR BOMBA OLEO AUDAX TITAN150 2004 A 2015/ FAN125 2009 A 2018/FAN150 2010/ CRF150F 2012 A 2017/ NXR150 2006 A 2015</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>7908429131431</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>RETOR BOMBA OLEO EMBUS TITAN FAN150 2004 A 2015/ BROS NXR150 2006 A 2015 11064-E</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>7908073705673</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>RETOR BOMBA OLEO SMARTFOX TITAN/ NX/ XR</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/BOMBA ÓLEO - 26_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/BOMBA ÓLEO - 26_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,7 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,11 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -574,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -599,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -624,7 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -645,7 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -666,11 +632,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -689,11 +650,6 @@
       <c r="D12" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
     </row>
